--- a/excel/Scramble Rima.xlsx
+++ b/excel/Scramble Rima.xlsx
@@ -5,28 +5,29 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Scramble\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Scramble\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1492CB0A-A6B7-4430-9981-9C7CF972E5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1709292-DE0D-449C-AC9E-3866557F6552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="15" r:id="rId2"/>
-    <sheet name="July 2026" sheetId="35" r:id="rId3"/>
-    <sheet name="June 2026" sheetId="34" r:id="rId4"/>
-    <sheet name="May 2026" sheetId="33" r:id="rId5"/>
-    <sheet name="April 2026" sheetId="32" r:id="rId6"/>
-    <sheet name="March 2026" sheetId="31" r:id="rId7"/>
-    <sheet name="February 2026" sheetId="30" r:id="rId8"/>
-    <sheet name="January 2026" sheetId="29" r:id="rId9"/>
-    <sheet name="December 2025" sheetId="28" r:id="rId10"/>
-    <sheet name="November 2025" sheetId="27" r:id="rId11"/>
-    <sheet name="October 2025" sheetId="26" r:id="rId12"/>
-    <sheet name="September 2025" sheetId="25" r:id="rId13"/>
-    <sheet name="August 2025" sheetId="14" r:id="rId14"/>
+    <sheet name="August 2026" sheetId="36" r:id="rId3"/>
+    <sheet name="July 2026" sheetId="35" r:id="rId4"/>
+    <sheet name="June 2026" sheetId="34" r:id="rId5"/>
+    <sheet name="May 2026" sheetId="33" r:id="rId6"/>
+    <sheet name="April 2026" sheetId="32" r:id="rId7"/>
+    <sheet name="March 2026" sheetId="31" r:id="rId8"/>
+    <sheet name="February 2026" sheetId="30" r:id="rId9"/>
+    <sheet name="January 2026" sheetId="29" r:id="rId10"/>
+    <sheet name="December 2025" sheetId="28" r:id="rId11"/>
+    <sheet name="November 2025" sheetId="27" r:id="rId12"/>
+    <sheet name="October 2025" sheetId="26" r:id="rId13"/>
+    <sheet name="September 2025" sheetId="25" r:id="rId14"/>
+    <sheet name="August 2025" sheetId="14" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="59">
   <si>
     <t>Paskola</t>
   </si>
@@ -224,6 +225,9 @@
   <si>
     <t>July 2026</t>
   </si>
+  <si>
+    <t>August 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -366,7 +370,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -448,6 +452,13 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -474,53 +485,11 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="68">
+  <dxfs count="56">
     <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -632,35 +601,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -716,35 +657,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -800,6 +713,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -842,6 +769,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -857,20 +798,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -985,7 +912,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D26DB4C-231C-4C87-87A9-E78886E7807B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C92B417E-0E73-40BA-95CB-0B8A5F160456}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1041,7 +968,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D9ED54-8C5F-4763-A103-EA86015ECDEF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B495DA4-2D50-43E7-92C9-52E679196A7D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1097,6 +1024,62 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D9ED54-8C5F-4763-A103-EA86015ECDEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD13F6DB-3617-4E16-85C6-CE67C2928B61}"/>
             </a:ext>
           </a:extLst>
@@ -1132,7 +1115,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1209,7 +1192,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13F58B75-E6DB-4D82-A45E-AB511FF3C881}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D26DB4C-231C-4C87-87A9-E78886E7807B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1265,7 +1248,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75ADCD55-EE0C-46E9-9BA6-6DDCE4741191}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13F58B75-E6DB-4D82-A45E-AB511FF3C881}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1321,7 +1304,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4516F9B9-44DD-4606-BEE5-CB1D2AAA0AF1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75ADCD55-EE0C-46E9-9BA6-6DDCE4741191}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1377,7 +1360,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2810C3BC-F093-4506-BBA0-6D497E73A3C1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4516F9B9-44DD-4606-BEE5-CB1D2AAA0AF1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1433,7 +1416,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D2C6C96-E314-400B-9CB5-8B0597A3C6F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2810C3BC-F093-4506-BBA0-6D497E73A3C1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1489,7 +1472,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB14DA99-6B92-49A0-A498-AA9896FB5940}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D2C6C96-E314-400B-9CB5-8B0597A3C6F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1545,7 +1528,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E2DBBC-C5B2-4288-AC0A-95368A14A86A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB14DA99-6B92-49A0-A498-AA9896FB5940}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1601,7 +1584,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B495DA4-2D50-43E7-92C9-52E679196A7D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E2DBBC-C5B2-4288-AC0A-95368A14A86A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1917,43 +1900,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="31" t="s">
+      <c r="A1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="34" t="s">
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="Q1" s="35" t="s">
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="Q1" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="35" t="s">
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="37"/>
-      <c r="W1" s="31" t="s">
+      <c r="V1" s="40"/>
+      <c r="W1" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="33"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
       <c r="AA1" s="4" t="s">
         <v>27</v>
       </c>
@@ -2109,7 +2092,7 @@
       </c>
       <c r="R3" s="28">
         <f>SUM(H3:H98)-U3</f>
-        <v>669.63999999999965</v>
+        <v>678.45999999999958</v>
       </c>
       <c r="S3" s="27">
         <f>Pinigai!H2</f>
@@ -2117,31 +2100,31 @@
       </c>
       <c r="T3" s="27">
         <f>W3-R3</f>
-        <v>0</v>
+        <v>3.0000000000427463E-2</v>
       </c>
       <c r="U3" s="28">
         <f>SUM(M3:M98)</f>
-        <v>925.92000000000007</v>
+        <v>1102.7800000000002</v>
       </c>
       <c r="V3" s="28">
         <f>SUM(N3:N98)-AA3</f>
-        <v>35.64</v>
+        <v>44.49</v>
       </c>
       <c r="W3" s="27">
         <f>Q3+S3+V3</f>
-        <v>669.64</v>
+        <v>678.49</v>
       </c>
       <c r="X3" s="27">
         <f>W3-Q3</f>
-        <v>59.639999999999986</v>
+        <v>68.490000000000009</v>
       </c>
       <c r="Y3" s="29">
         <f>(W3-Q3)/Q3</f>
-        <v>9.7770491803278667E-2</v>
+        <v>0.11227868852459018</v>
       </c>
       <c r="Z3" s="30">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>1.1269685626029969E-2</v>
+        <v>0.12073680758476255</v>
       </c>
       <c r="AA3" s="27">
         <f>SUM(O3:O98)</f>
@@ -2528,13 +2511,13 @@
         <f>'February 2026'!B11</f>
         <v>46239</v>
       </c>
-      <c r="J9" s="6" t="str">
+      <c r="J9" s="6">
         <f>'February 2026'!O3</f>
-        <v/>
-      </c>
-      <c r="K9" s="18">
+        <v>46239</v>
+      </c>
+      <c r="K9" s="18" t="str">
         <f ca="1">'February 2026'!B12</f>
-        <v>4</v>
+        <v/>
       </c>
       <c r="L9" s="18" t="str">
         <f ca="1">'February 2026'!P3</f>
@@ -2542,11 +2525,11 @@
       </c>
       <c r="M9" s="3">
         <f>'February 2026'!K3</f>
-        <v>54.099999999999994</v>
+        <v>198.85</v>
       </c>
       <c r="N9" s="3">
         <f>'February 2026'!L3</f>
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="O9" s="3">
         <f>'February 2026'!M3</f>
@@ -2600,7 +2583,7 @@
       </c>
       <c r="K10" s="18">
         <f ca="1">'March 2026'!B12</f>
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L10" s="18" t="str">
         <f ca="1">'March 2026'!P3</f>
@@ -2608,7 +2591,7 @@
       </c>
       <c r="M10" s="3">
         <f>'March 2026'!K3</f>
-        <v>38.479999999999997</v>
+        <v>47.8</v>
       </c>
       <c r="N10" s="3">
         <f>'March 2026'!L3</f>
@@ -2666,7 +2649,7 @@
       </c>
       <c r="K11" s="18">
         <f ca="1">'April 2026'!B12</f>
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="L11" s="18" t="str">
         <f ca="1">'April 2026'!P3</f>
@@ -2674,7 +2657,7 @@
       </c>
       <c r="M11" s="3">
         <f>'April 2026'!K3</f>
-        <v>32.400000000000006</v>
+        <v>43.2</v>
       </c>
       <c r="N11" s="3">
         <f>'April 2026'!L3</f>
@@ -2732,7 +2715,7 @@
       </c>
       <c r="K12" s="18">
         <f ca="1">'May 2026'!B12</f>
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="L12" s="18" t="str">
         <f ca="1">'May 2026'!P3</f>
@@ -2740,7 +2723,7 @@
       </c>
       <c r="M12" s="3">
         <f>'May 2026'!K3</f>
-        <v>12.26</v>
+        <v>18.39</v>
       </c>
       <c r="N12" s="3">
         <f>'May 2026'!L3</f>
@@ -2797,7 +2780,7 @@
       </c>
       <c r="K13" s="18">
         <f ca="1">'June 2026'!B12</f>
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="L13" s="18" t="str">
         <f ca="1">'June 2026'!P3</f>
@@ -2805,7 +2788,7 @@
       </c>
       <c r="M13" s="3">
         <f>'June 2026'!K3</f>
-        <v>4.1399999999999997</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="N13" s="3">
         <f>'June 2026'!L3</f>
@@ -2862,7 +2845,7 @@
       </c>
       <c r="K14" s="18">
         <f ca="1">'July 2026'!B12</f>
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="L14" s="18" t="str">
         <f ca="1">'July 2026'!P3</f>
@@ -2870,7 +2853,7 @@
       </c>
       <c r="M14" s="3">
         <f>'July 2026'!K3</f>
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="N14" s="3">
         <f>'July 2026'!L3</f>
@@ -2886,22 +2869,69 @@
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="AC15" s="1"/>
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="6">
+        <f>'August 2026'!B9</f>
+        <v>46241</v>
+      </c>
+      <c r="C15" s="24" t="str">
+        <f>'August 2026'!B1</f>
+        <v>August 2026</v>
+      </c>
+      <c r="D15" s="2" t="str">
+        <f>'August 2026'!B2</f>
+        <v>Estonia</v>
+      </c>
+      <c r="E15" s="2" t="str">
+        <f>'August 2026'!B3</f>
+        <v>Scramble</v>
+      </c>
+      <c r="F15" s="2" t="str">
+        <f>'August 2026'!B8</f>
+        <v>0 m. 5 mėn. 29 d.</v>
+      </c>
+      <c r="G15" s="7" t="str">
+        <f>'August 2026'!B15</f>
+        <v>9-12%</v>
+      </c>
+      <c r="H15" s="3">
+        <f>'August 2026'!B16</f>
+        <v>185.68</v>
+      </c>
+      <c r="I15" s="6">
+        <f>'August 2026'!B11</f>
+        <v>46423</v>
+      </c>
+      <c r="J15" s="6" t="str">
+        <f>'August 2026'!O3</f>
+        <v/>
+      </c>
+      <c r="K15" s="18">
+        <f ca="1">'August 2026'!B12</f>
+        <v>180</v>
+      </c>
+      <c r="L15" s="18" t="str">
+        <f ca="1">'August 2026'!P3</f>
+        <v/>
+      </c>
+      <c r="M15" s="3">
+        <f>'August 2026'!K3</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <f>'August 2026'!L3</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <f>'August 2026'!M3</f>
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3" t="str">
+        <f ca="1">'August 2026'!Z3</f>
+        <v/>
+      </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -3093,20 +3123,20 @@
     <mergeCell ref="U1:V1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:O25">
-    <cfRule type="expression" dxfId="67" priority="9">
+    <cfRule type="expression" dxfId="55" priority="9">
       <formula>$AC3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="13">
+    <cfRule type="expression" dxfId="54" priority="13">
       <formula>AND($H3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC3:AC25">
-    <cfRule type="expression" dxfId="65" priority="2">
+    <cfRule type="expression" dxfId="53" priority="2">
       <formula>AND($H3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC6:AC14">
-    <cfRule type="expression" dxfId="64" priority="1">
+  <conditionalFormatting sqref="AC6:AC15">
+    <cfRule type="expression" dxfId="52" priority="1">
       <formula>$AC6="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3123,6 +3153,7 @@
     <hyperlink ref="C12" location="'May 2026'!A1" display="'May 2026'!A1" xr:uid="{245E7DBA-D947-40F8-8F15-9915FFE1DD5E}"/>
     <hyperlink ref="C13" location="'June 2026'!A1" display="'June 2026'!A1" xr:uid="{D41A3630-A56F-4916-B1AA-C5C3695F19A8}"/>
     <hyperlink ref="C14" location="'July 2026'!A1" display="'July 2026'!A1" xr:uid="{8B58AC79-8F19-4849-BA55-1D38985B2EEB}"/>
+    <hyperlink ref="C15" location="'August 2026'!A1" display="'August 2026'!A1" xr:uid="{6EA87317-B9C8-43E4-8AE8-6D1BF358572F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3130,6 +3161,1338 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E465F013-9FF2-44FD-828F-D999C3230D4E}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="13" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="13" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46058</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46058</v>
+      </c>
+      <c r="F3" s="18">
+        <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="13"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>39.949999999999996</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>1.77</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v>0.10611786246299745</v>
+      </c>
+      <c r="O3" s="6">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v>46209</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v>0</v>
+      </c>
+      <c r="T3" s="15"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46027</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-39.950000000000003</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="6">
+        <v>46086</v>
+      </c>
+      <c r="E4" s="6">
+        <v>46086</v>
+      </c>
+      <c r="F4" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46058</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>2.2599999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="6">
+        <v>46118</v>
+      </c>
+      <c r="E5" s="6">
+        <v>46118</v>
+      </c>
+      <c r="F5" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>46086</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>2.2599999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="6">
+        <v>46147</v>
+      </c>
+      <c r="E6" s="6">
+        <v>46147</v>
+      </c>
+      <c r="F6" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>46118</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>2.2599999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="6">
+        <v>46178</v>
+      </c>
+      <c r="E7" s="6">
+        <v>46178</v>
+      </c>
+      <c r="F7" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>46147</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>2.2599999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 6 mėn. 1 d.</v>
+      </c>
+      <c r="D8" s="6">
+        <v>46209</v>
+      </c>
+      <c r="E8" s="6">
+        <v>46209</v>
+      </c>
+      <c r="F8" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>28.65</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1.77</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>46178</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>2.2599999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46027</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="13"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>46209</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>30.419999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46039</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="13"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46209</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="13"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="18" t="str">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="13"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="13"/>
+      <c r="N13" s="15"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="19"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="13"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="3">
+        <v>39.950000000000003</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="10"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="13"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="13"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="13"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="10"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="13"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="10"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="13"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="10"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="13"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="10"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="13"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="10"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="13"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="10"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="13"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="10"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="13"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="10"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="13"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="10"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="13"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="10"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="13"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="10"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="13"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="10"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="13"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="10"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="13"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="10"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="13"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="13"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="10"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="13"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="10"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="13"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="13"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="13"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="13"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="13"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="13"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="13"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="13"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="13"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="13"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="13"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="10"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="13"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="10"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="13"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="10"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="13"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="10"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="13"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="10"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="13"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="10"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>39.949999999999996</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>1.77</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="23" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="21" priority="7">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="20" priority="8">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D1CAB2-9974-4180-AFF6-5274525FE544}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -3159,29 +4522,29 @@
       <c r="B1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="33"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="33"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -4432,20 +5795,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="2">
+    <cfRule type="expression" dxfId="18" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="19" priority="7">
+    <cfRule type="expression" dxfId="17" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="18" priority="8">
+    <cfRule type="expression" dxfId="16" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4455,7 +5818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3754DA4B-78B4-44BD-BB4B-39C6D453FDD0}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4485,29 +5848,29 @@
       <c r="B1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="33"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="33"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -5758,20 +7121,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="15" priority="7">
+    <cfRule type="expression" dxfId="13" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="14" priority="8">
+    <cfRule type="expression" dxfId="12" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5781,7 +7144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A46497B-E391-4B8F-8947-28547C504629}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -5811,29 +7174,29 @@
       <c r="B1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="33"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="33"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -7077,30 +8440,22 @@
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="13" priority="3">
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="4">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="11" priority="10">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="8" priority="11">
       <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="9" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="2">
-      <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7109,7 +8464,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE44972-B3BE-4780-9CE5-89011043CB83}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -7139,29 +8494,29 @@
       <c r="B1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="33"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="33"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -8429,7 +9784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -8459,29 +9814,29 @@
       <c r="B1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="33"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="33"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -9751,7 +11106,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K200"/>
+  <dimension ref="A1:O200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="21" customWidth="1"/>
@@ -9759,7 +11114,7 @@
     <col min="6" max="9" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -9788,9 +11143,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>38576</v>
+        <v>45881</v>
       </c>
       <c r="B2" s="3">
         <v>205</v>
@@ -9821,8 +11176,9 @@
         <f>B2*-1</f>
         <v>-205</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="O2" s="33"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>45881</v>
       </c>
@@ -9840,9 +11196,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>38577</v>
+        <v>45882</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -9858,7 +11214,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>45889</v>
       </c>
@@ -9876,7 +11232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>45898</v>
       </c>
@@ -9894,7 +11250,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>45917</v>
       </c>
@@ -9912,7 +11268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>45929</v>
       </c>
@@ -9930,7 +11286,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>45947</v>
       </c>
@@ -9948,185 +11304,131 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
-      <c r="K10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="K11" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
-      <c r="K12" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="K13" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
-      <c r="K14" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
-      <c r="K15" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
-      <c r="K16" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="K16" s="3"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
-      <c r="K17" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="K17" s="3"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
-      <c r="K18" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="K18" s="3"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
-      <c r="K19" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="K19" s="3"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
-      <c r="K20" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="K20" s="3"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
-      <c r="K21" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="K21" s="3"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
-      <c r="K22" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="K22" s="3"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="2"/>
-      <c r="K23" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="K23" s="3"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
-      <c r="K24" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="K24" s="3"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
-      <c r="K25" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="K25" s="3"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
-      <c r="K26" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="K26" s="3"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="K27" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="K27" s="3"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
@@ -11335,14 +12637,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <f ca="1">TODAY()</f>
-        <v>46235</v>
+        <v>46243</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="25">
         <f>Overview!W3</f>
-        <v>669.64</v>
+        <v>678.49</v>
       </c>
     </row>
   </sheetData>
@@ -11351,6 +12653,1290 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E5D5DD-CBD2-4FD8-9F41-16B9523FDC2D}">
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="13" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="13" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="X2" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z2" s="32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46270</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="18" t="str">
+        <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="15"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46241</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-185.68</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="6">
+        <v>46300</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="6">
+        <v>46331</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="6">
+        <v>46361</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="6">
+        <v>46392</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="13"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 5 mėn. 29 d.</v>
+      </c>
+      <c r="D8" s="6">
+        <v>46423</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46241</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="13"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46251</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="13"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46423</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="13"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="18">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v>180</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="13"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="13"/>
+      <c r="N13" s="15"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="19"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="13"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="3">
+        <v>185.68</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="10"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="13"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="13"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="13"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="10"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="13"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="10"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="13"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="10"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="13"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="10"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="13"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="10"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="13"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="10"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="13"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="10"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="13"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="10"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="13"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="10"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="13"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="10"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="13"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="10"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="13"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="10"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="13"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="10"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="13"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="10"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="13"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="13"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="10"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="13"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="10"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="13"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="13"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="13"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="13"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="13"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="13"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="13"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="13"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="13"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="13"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="13"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="10"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="13"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="10"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="13"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="10"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="13"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="10"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="13"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="10"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="13"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="10"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="51" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="49" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="48" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EA74071-CEE0-4172-8957-6D5916CFD11C}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11377,29 +13963,29 @@
       <c r="B1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="33"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="33"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -11468,18 +14054,26 @@
       <c r="D3" s="6">
         <v>46239</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="18" t="str">
+      <c r="E3" s="6">
+        <v>46239</v>
+      </c>
+      <c r="F3" s="18">
         <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.72</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
@@ -11540,11 +14134,11 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46239</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -11732,7 +14326,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -12592,7 +15186,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
@@ -12610,30 +15204,22 @@
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="63" priority="3">
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="4">
+    <cfRule type="expression" dxfId="46" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="61" priority="7">
+    <cfRule type="expression" dxfId="45" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="60" priority="8">
+    <cfRule type="expression" dxfId="44" priority="8">
       <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="59" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="2">
-      <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12642,7 +15228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E39A4C94-8C03-41D4-B944-5DB24FED2BD0}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12669,29 +15255,29 @@
       <c r="B1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="33"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="33"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -12779,7 +15365,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>4.1399999999999997</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
@@ -12829,14 +15415,21 @@
       <c r="D4" s="6">
         <v>46239</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="E4" s="6">
+        <v>46239</v>
+      </c>
+      <c r="F4" s="18">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -12864,11 +15457,11 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
+        <v>46239</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
+        <v>4.1399999999999997</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -13032,7 +15625,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -13892,7 +16485,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>4.1399999999999997</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
@@ -13910,30 +16503,22 @@
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="57" priority="3">
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="4">
+    <cfRule type="expression" dxfId="42" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="55" priority="7">
+    <cfRule type="expression" dxfId="41" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="54" priority="8">
+    <cfRule type="expression" dxfId="40" priority="8">
       <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="53" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="2">
-      <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13942,7 +16527,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51596B63-3E30-4F0D-ACA7-3B11B25E71A9}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13969,29 +16554,29 @@
       <c r="B1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="33"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="33"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -14079,7 +16664,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>12.26</v>
+        <v>18.39</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
@@ -14161,14 +16746,22 @@
       <c r="D5" s="6">
         <v>46239</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="E5" s="6">
+        <v>46239</v>
+      </c>
+      <c r="F5" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>6.13</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
@@ -14196,11 +16789,11 @@
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46239</v>
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -14340,7 +16933,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -15200,7 +17793,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>12.26</v>
+        <v>18.39</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
@@ -15218,30 +17811,22 @@
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="51" priority="3">
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="4">
+    <cfRule type="expression" dxfId="38" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="49" priority="7">
+    <cfRule type="expression" dxfId="37" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="48" priority="8">
+    <cfRule type="expression" dxfId="36" priority="8">
       <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="47" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="2">
-      <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15250,7 +17835,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6787A89-4537-4E64-91BF-0AA0F96019C3}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15277,29 +17862,29 @@
       <c r="B1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="33"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="33"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -15387,7 +17972,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>32.400000000000006</v>
+        <v>43.2</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
@@ -15501,14 +18086,22 @@
       <c r="D6" s="6">
         <v>46239</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="E6" s="6">
+        <v>46239</v>
+      </c>
+      <c r="F6" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>10.8</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
@@ -15536,11 +18129,11 @@
       <c r="J7" s="13"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46239</v>
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -15656,7 +18249,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -16516,7 +19109,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>32.400000000000006</v>
+        <v>43.2</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
@@ -16534,30 +19127,22 @@
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="45" priority="3">
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="4">
+    <cfRule type="expression" dxfId="34" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="43" priority="7">
+    <cfRule type="expression" dxfId="33" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="42" priority="8">
+    <cfRule type="expression" dxfId="32" priority="8">
       <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="41" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="2">
-      <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16566,7 +19151,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B83440-5743-4944-A92C-7C00476AA6BD}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16593,29 +19178,29 @@
       <c r="B1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="33"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="33"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -16703,7 +19288,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>38.479999999999997</v>
+        <v>47.8</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
@@ -16849,14 +19434,22 @@
       <c r="D7" s="6">
         <v>46239</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="E7" s="6">
+        <v>46239</v>
+      </c>
+      <c r="F7" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>9.32</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
       <c r="J7" s="13"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
@@ -16889,11 +19482,11 @@
       <c r="J8" s="9"/>
       <c r="X8" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46239</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -16980,7 +19573,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -17840,7 +20433,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>38.479999999999997</v>
+        <v>47.8</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
@@ -17858,1361 +20451,22 @@
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="39" priority="3">
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="4">
+    <cfRule type="expression" dxfId="30" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="37" priority="7">
+    <cfRule type="expression" dxfId="29" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="36" priority="8">
+    <cfRule type="expression" dxfId="28" priority="8">
       <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="35" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="2">
-      <formula>$B$16=$K$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8F9EBE-D214-44A2-8A19-768E491F391C}">
-  <dimension ref="A1:Z53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="23" width="8.7109375" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="13" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" style="13" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="33"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="33"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="6">
-        <v>46086</v>
-      </c>
-      <c r="E3" s="6">
-        <v>46086</v>
-      </c>
-      <c r="F3" s="18">
-        <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>10.86</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="3">
-        <f>G53</f>
-        <v>54.099999999999994</v>
-      </c>
-      <c r="L3" s="3">
-        <f>H53</f>
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
-        <f>I53</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="6" t="str">
-        <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v/>
-      </c>
-      <c r="P3" s="2" t="str">
-        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="2" t="str">
-        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v/>
-      </c>
-      <c r="T3" s="15"/>
-      <c r="X3" s="6">
-        <f>B9</f>
-        <v>46058</v>
-      </c>
-      <c r="Y3" s="3">
-        <f>B16*-1</f>
-        <v>-198.85</v>
-      </c>
-      <c r="Z3" s="2" t="str">
-        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="6">
-        <v>46118</v>
-      </c>
-      <c r="E4" s="6">
-        <v>46118</v>
-      </c>
-      <c r="F4" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>10.76</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0</v>
-      </c>
-      <c r="J4" s="9"/>
-      <c r="X4" s="6">
-        <f>E3</f>
-        <v>46086</v>
-      </c>
-      <c r="Y4" s="3">
-        <f>G3+H3-I3</f>
-        <v>10.86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="D5" s="6">
-        <v>46147</v>
-      </c>
-      <c r="E5" s="6">
-        <v>46147</v>
-      </c>
-      <c r="F5" s="18">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>10.96</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9"/>
-      <c r="X5" s="6">
-        <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>46118</v>
-      </c>
-      <c r="Y5" s="3">
-        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>10.76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="D6" s="6">
-        <v>46178</v>
-      </c>
-      <c r="E6" s="6">
-        <v>46178</v>
-      </c>
-      <c r="F6" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>10.76</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="X6" s="6">
-        <f t="shared" si="1"/>
-        <v>46147</v>
-      </c>
-      <c r="Y6" s="3">
-        <f t="shared" si="2"/>
-        <v>10.96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="D7" s="6">
-        <v>46209</v>
-      </c>
-      <c r="E7" s="6">
-        <v>46209</v>
-      </c>
-      <c r="F7" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>10.76</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
-      <c r="J7" s="13"/>
-      <c r="X7" s="6">
-        <f t="shared" si="1"/>
-        <v>46178</v>
-      </c>
-      <c r="Y7" s="3">
-        <f t="shared" si="2"/>
-        <v>10.76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="6" t="str">
-        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 6 mėn. 0 d.</v>
-      </c>
-      <c r="D8" s="6">
-        <v>46239</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="9"/>
-      <c r="X8" s="6">
-        <f t="shared" si="1"/>
-        <v>46209</v>
-      </c>
-      <c r="Y8" s="3">
-        <f t="shared" si="2"/>
-        <v>10.76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46058</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="13"/>
-      <c r="X9" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="6">
-        <v>46070</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="13"/>
-      <c r="X10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <v>46239</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="13"/>
-      <c r="X11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="18">
-        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>4</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="13"/>
-      <c r="X12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="3"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="13"/>
-      <c r="N13" s="15"/>
-      <c r="X13" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="19"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="13"/>
-      <c r="X14" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="X15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="3">
-        <v>198.85</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="X16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D17" s="10"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="13"/>
-      <c r="X17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D18" s="10"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="13"/>
-      <c r="X18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D19" s="10"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="13"/>
-      <c r="X19" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D20" s="10"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="13"/>
-      <c r="X20" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D21" s="10"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="13"/>
-      <c r="X21" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D22" s="10"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="13"/>
-      <c r="X22" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D23" s="10"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="13"/>
-      <c r="X23" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D24" s="10"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="13"/>
-      <c r="X24" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D25" s="10"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="13"/>
-      <c r="X25" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D26" s="10"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="13"/>
-      <c r="X26" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D27" s="10"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="13"/>
-      <c r="X27" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D28" s="10"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="13"/>
-      <c r="X28" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D29" s="10"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="13"/>
-      <c r="X29" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D30" s="10"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="13"/>
-      <c r="X30" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D31" s="10"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="13"/>
-      <c r="X31" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D32" s="10"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="13"/>
-      <c r="X32" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D33" s="10"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="13"/>
-      <c r="X33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D34" s="10"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="13"/>
-      <c r="X34" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D35" s="10"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="13"/>
-      <c r="X35" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D36" s="10"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="13"/>
-      <c r="X36" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D37" s="10"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="13"/>
-      <c r="X37" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D38" s="10"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="13"/>
-      <c r="X38" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D39" s="10"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="13"/>
-      <c r="X39" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D40" s="10"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="13"/>
-      <c r="X40" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y40" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D41" s="10"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="13"/>
-      <c r="X41" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D42" s="10"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="13"/>
-      <c r="X42" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D43" s="10"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="13"/>
-      <c r="X43" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D44" s="10"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="13"/>
-      <c r="X44" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D45" s="10"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="13"/>
-      <c r="X45" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D46" s="10"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="13"/>
-      <c r="X46" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D47" s="10"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="13"/>
-      <c r="X47" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D48" s="10"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="13"/>
-      <c r="X48" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D49" s="10"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="13"/>
-      <c r="X49" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D50" s="10"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="13"/>
-      <c r="X50" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y50" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D51" s="10"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="13"/>
-      <c r="X51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D52" s="10"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="9"/>
-      <c r="X52" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D53" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E53" s="14"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3">
-        <f>SUM(G3:G52)</f>
-        <v>54.099999999999994</v>
-      </c>
-      <c r="H53" s="3">
-        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
-      </c>
-      <c r="I53" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="X1:Z1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="33" priority="3">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="4">
-      <formula>$B$16=$K$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="31" priority="9">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="30" priority="10">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="29" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="2">
-      <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19222,7 +20476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E465F013-9FF2-44FD-828F-D999C3230D4E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8F9EBE-D214-44A2-8A19-768E491F391C}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
@@ -19249,31 +20503,31 @@
         <v>28</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="33"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="33"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -19340,17 +20594,17 @@
         <v>42</v>
       </c>
       <c r="D3" s="6">
-        <v>46058</v>
+        <v>46086</v>
       </c>
       <c r="E3" s="6">
-        <v>46058</v>
+        <v>46086</v>
       </c>
       <c r="F3" s="18">
         <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>2.2599999999999998</v>
+        <v>10.86</v>
       </c>
       <c r="H3" s="3">
         <v>0</v>
@@ -19361,11 +20615,11 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>39.949999999999996</v>
+        <v>198.85</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>1.77</v>
+        <v>8.85</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -19373,11 +20627,11 @@
       </c>
       <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.10611786246299745</v>
+        <v>0.10662775635719302</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v>46209</v>
+        <v>46239</v>
       </c>
       <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
@@ -19390,11 +20644,11 @@
       <c r="T3" s="15"/>
       <c r="X3" s="6">
         <f>B9</f>
-        <v>46027</v>
+        <v>46058</v>
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-39.950000000000003</v>
+        <v>-198.85</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -19409,17 +20663,17 @@
         <v>44</v>
       </c>
       <c r="D4" s="6">
-        <v>46086</v>
+        <v>46118</v>
       </c>
       <c r="E4" s="6">
-        <v>46086</v>
+        <v>46118</v>
       </c>
       <c r="F4" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>2.2599999999999998</v>
+        <v>10.76</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
@@ -19430,28 +20684,27 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>46058</v>
+        <v>46086</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>2.2599999999999998</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
       <c r="D5" s="6">
-        <v>46118</v>
+        <v>46147</v>
       </c>
       <c r="E5" s="6">
-        <v>46118</v>
+        <v>46147</v>
       </c>
       <c r="F5" s="18">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>2.2599999999999998</v>
+        <v>10.96</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
@@ -19462,28 +20715,28 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>46086</v>
+        <v>46118</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>2.2599999999999998</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="D6" s="6">
-        <v>46147</v>
+        <v>46178</v>
       </c>
       <c r="E6" s="6">
-        <v>46147</v>
+        <v>46178</v>
       </c>
       <c r="F6" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>2.2599999999999998</v>
+        <v>10.76</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
@@ -19494,28 +20747,28 @@
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
-        <v>46118</v>
+        <v>46147</v>
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>2.2599999999999998</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="D7" s="6">
-        <v>46178</v>
+        <v>46209</v>
       </c>
       <c r="E7" s="6">
-        <v>46178</v>
+        <v>46209</v>
       </c>
       <c r="F7" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>2.2599999999999998</v>
+        <v>10.76</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
@@ -19526,11 +20779,11 @@
       <c r="J7" s="13"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
-        <v>46147</v>
+        <v>46178</v>
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>2.2599999999999998</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -19539,23 +20792,23 @@
       </c>
       <c r="B8" s="6" t="str">
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 6 mėn. 1 d.</v>
+        <v>0 m. 6 mėn. 0 d.</v>
       </c>
       <c r="D8" s="6">
-        <v>46209</v>
+        <v>46239</v>
       </c>
       <c r="E8" s="6">
-        <v>46209</v>
+        <v>46239</v>
       </c>
       <c r="F8" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>28.65</v>
+        <v>144.75</v>
       </c>
       <c r="H8" s="3">
-        <v>1.77</v>
+        <v>8.85</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -19563,11 +20816,11 @@
       <c r="J8" s="9"/>
       <c r="X8" s="6">
         <f t="shared" si="1"/>
-        <v>46178</v>
+        <v>46209</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>2.2599999999999998</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -19575,22 +20828,25 @@
         <v>9</v>
       </c>
       <c r="B9" s="6">
-        <v>46027</v>
+        <v>46058</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="3"/>
+      <c r="F9" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="2"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="13"/>
       <c r="X9" s="6">
         <f t="shared" si="1"/>
-        <v>46209</v>
+        <v>46239</v>
       </c>
       <c r="Y9" s="3">
         <f t="shared" si="2"/>
-        <v>30.419999999999998</v>
+        <v>153.6</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -19598,7 +20854,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="6">
-        <v>46039</v>
+        <v>46070</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
@@ -19624,7 +20880,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="6">
-        <v>46209</v>
+        <v>46239</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -19755,7 +21011,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3">
-        <v>39.950000000000003</v>
+        <v>198.85</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="6"/>
@@ -20511,11 +21767,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>39.949999999999996</v>
+        <v>198.85</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1.77</v>
+        <v>8.85</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -20529,30 +21785,22 @@
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="27" priority="3">
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="4">
+    <cfRule type="expression" dxfId="26" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="25" priority="7">
+    <cfRule type="expression" dxfId="25" priority="9">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="24" priority="8">
+    <cfRule type="expression" dxfId="24" priority="10">
       <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="23" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="2">
-      <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/Scramble Rima.xlsx
+++ b/excel/Scramble Rima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Scramble\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1709292-DE0D-449C-AC9E-3866557F6552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93A0626-5D33-4C9A-B0A5-F271A001999A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z3" s="30">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.12073680758476255</v>
+        <v>0.11268935799598695</v>
       </c>
       <c r="AA3" s="27">
         <f>SUM(O3:O98)</f>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="K10" s="18">
         <f ca="1">'March 2026'!B12</f>
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="L10" s="18" t="str">
         <f ca="1">'March 2026'!P3</f>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="K11" s="18">
         <f ca="1">'April 2026'!B12</f>
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L11" s="18" t="str">
         <f ca="1">'April 2026'!P3</f>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K12" s="18">
         <f ca="1">'May 2026'!B12</f>
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="L12" s="18" t="str">
         <f ca="1">'May 2026'!P3</f>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="K13" s="18">
         <f ca="1">'June 2026'!B12</f>
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="L13" s="18" t="str">
         <f ca="1">'June 2026'!P3</f>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="K14" s="18">
         <f ca="1">'July 2026'!B12</f>
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="L14" s="18" t="str">
         <f ca="1">'July 2026'!P3</f>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="K15" s="18">
         <f ca="1">'August 2026'!B12</f>
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="L15" s="18" t="str">
         <f ca="1">'August 2026'!P3</f>
@@ -11192,7 +11192,7 @@
         <v>10</v>
       </c>
       <c r="K3" s="3">
-        <f t="shared" ref="K3:K27" si="0">B3*-1</f>
+        <f t="shared" ref="K3:K9" si="0">B3*-1</f>
         <v>0</v>
       </c>
     </row>
@@ -12637,7 +12637,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46266</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -14326,7 +14326,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -15625,7 +15625,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -18249,7 +18249,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
